--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC1F115-3B5A-4139-9493-31DFB62B1AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE69757A-94AE-44EB-9307-7E07E376F4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="1124">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3397,6 +3397,9 @@
   </si>
   <si>
     <t>SERVO HYPERDRIVE 5W-30-4X3.5 L PROMO</t>
+  </si>
+  <si>
+    <t>ECSTAR PETROL 0W-16 FE-4 X 3.5 L</t>
   </si>
 </sst>
 </file>
@@ -3440,7 +3443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -3757,7 +3760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1131"/>
+  <dimension ref="A1:C1132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16206,6 +16209,17 @@
         <v>14</v>
       </c>
     </row>
+    <row r="1132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1132" s="1">
+        <v>7079213</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C1132" s="1">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE69757A-94AE-44EB-9307-7E07E376F4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBED9A7-ADC9-401C-B1AB-59EFFF4B000D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="1125">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3400,6 +3400,9 @@
   </si>
   <si>
     <t>ECSTAR PETROL 0W-16 FE-4 X 3.5 L</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE 20W-40-4 X 5 L PROMO</t>
   </si>
 </sst>
 </file>
@@ -3760,7 +3763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1132"/>
+  <dimension ref="A1:C1133"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16220,6 +16223,17 @@
         <v>14</v>
       </c>
     </row>
+    <row r="1133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1133" s="1">
+        <v>475920240</v>
+      </c>
+      <c r="B1133" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C1133" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBED9A7-ADC9-401C-B1AB-59EFFF4B000D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709177A3-8226-413F-A6A6-256745AA7F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="1129">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3403,6 +3403,18 @@
   </si>
   <si>
     <t>SERVO PRIDE 20W-40-4 X 5 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE TC 15W-40-20 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE XL PLUS 15W-40.-20 X 1 L</t>
+  </si>
+  <si>
+    <t>SERVO ZOOM 4T-20 X 1 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE TC 15W-40-15 L PROMO</t>
   </si>
 </sst>
 </file>
@@ -3763,7 +3775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1133"/>
+  <dimension ref="A1:C1137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16224,14 +16236,58 @@
       </c>
     </row>
     <row r="1133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1133" s="1">
+      <c r="A1133">
         <v>475920240</v>
       </c>
-      <c r="B1133" s="1" t="s">
+      <c r="B1133" t="s">
         <v>1124</v>
       </c>
       <c r="C1133" s="1">
         <v>20</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1134" s="1">
+        <v>482340269</v>
+      </c>
+      <c r="B1134" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C1134" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1135" s="1">
+        <v>473750184</v>
+      </c>
+      <c r="B1135" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C1135" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1136" s="1">
+        <v>429240229</v>
+      </c>
+      <c r="B1136" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C1136" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1137" s="1">
+        <v>482340253</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C1137" s="1">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709177A3-8226-413F-A6A6-256745AA7F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399C2EEF-4853-4C23-AC67-9230EA31EE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="1134">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3415,6 +3415,21 @@
   </si>
   <si>
     <t>SERVO PRIDE TC 15W-40-15 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO FUTURA 5W-30-4X3.5 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE 15W-40-10 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE 15W-40-4 X 5 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE TC 15W-40-7.5 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO PRIDE TC 15W-40-10 L PROMO</t>
   </si>
 </sst>
 </file>
@@ -3775,7 +3790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1903B9F1-43DC-44BD-B1E4-00910B416442}">
-  <dimension ref="A1:C1137"/>
+  <dimension ref="A1:C1144"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -16290,6 +16305,75 @@
         <v>15</v>
       </c>
     </row>
+    <row r="1138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1138">
+        <v>474300111</v>
+      </c>
+      <c r="B1138" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C1138" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1139">
+        <v>475770241</v>
+      </c>
+      <c r="B1139" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C1139" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1140">
+        <v>482340253</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C1140" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1141">
+        <v>475770240</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C1141" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1142">
+        <v>482340250</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C1142" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1143">
+        <v>482340241</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C1143" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1144"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Advance Stock/UOM.xlsx
+++ b/Advance Stock/UOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Advance Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399C2EEF-4853-4C23-AC67-9230EA31EE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F60E8FC-5E12-47FC-B96E-E11660E52800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65A185-A3B8-4AF1-905D-A5939FA8F4CD}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="1135">
   <si>
     <t>SKU Name</t>
   </si>
@@ -3430,6 +3430,9 @@
   </si>
   <si>
     <t>SERVO PRIDE TC 15W-40-10 L PROMO</t>
+  </si>
+  <si>
+    <t>SERVO ZOOM 2T SUPREME-20 X 1/2 L</t>
   </si>
 </sst>
 </file>
@@ -16372,7 +16375,15 @@
       </c>
     </row>
     <row r="1144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1144"/>
+      <c r="A1144">
+        <v>429000175</v>
+      </c>
+      <c r="B1144" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C1144" s="1">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
